--- a/data/trans_orig/IP07_A12_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07_A12_2023-Habitat-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de estar demasiado cansado/a para disfrutar de las cosas que le gustan, percibida por el adulto en 2023 (tasa de respuesta: 99,9%)</t>
+          <t>Menores según la frecuencia de estar demasiado cansado/a para disfrutar de las cosas que le gustan, percibida por el/la adulto/a en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2903</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>532</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8584</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,68%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>10,89%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3073</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>802</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7470</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5,29%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>12,85%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2726</t>
+          <t>3368</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>1069</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8451</t>
+          <t>8534</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>5799</t>
+          <t>6271</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2279</t>
+          <t>2393</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12354</t>
+          <t>13107</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>9,25%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1182</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4128</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>5,24%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1687</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>385</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4693</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2,9%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>8,07%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1181</t>
+          <t>1846</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>344</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3727</t>
+          <t>5642</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>2868</t>
+          <t>3027</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>938</t>
+          <t>1099</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6517</t>
+          <t>7642</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4674</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1625</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>11558</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>5,93%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>14,66%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2842</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>705</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6796</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,89%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>11,69%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9654</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2110</t>
+          <t>864</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28471</t>
+          <t>7653</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>12496</t>
+          <t>7696</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4976</t>
+          <t>3744</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>33550</t>
+          <t>15341</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>10,82%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>13756</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8082</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>21745</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>17,45%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>10,25%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>27,59%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>11260</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>6475</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>16627</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>19,38%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>11,14%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>28,61%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13533</t>
+          <t>11959</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7303</t>
+          <t>6981</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21357</t>
+          <t>18261</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>24793</t>
+          <t>25715</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16635</t>
+          <t>18359</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34421</t>
+          <t>36590</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>25,82%</t>
         </is>
       </c>
     </row>
@@ -1172,72 +1172,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>56307</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>47655</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>65006</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>71,44%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>60,46%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>82,47%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>39250</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>33165</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>45087</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>67,54%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>57,07%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>77,59%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>57980</t>
+          <t>42708</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>45320</t>
+          <t>35551</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>68924</t>
+          <t>48744</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>97231</t>
+          <t>99016</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>83218</t>
+          <t>88344</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>110478</t>
+          <t>109478</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>69,86%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>77,25%</t>
         </is>
       </c>
     </row>
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>78821</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>78821</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>78821</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>58113</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>58113</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>58113</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>85074</t>
+          <t>62904</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>85074</t>
+          <t>62904</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>85074</t>
+          <t>62904</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>143187</t>
+          <t>141725</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>143187</t>
+          <t>141725</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>143187</t>
+          <t>141725</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3814</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>972</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10324</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,59%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7,01%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4892</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1930</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9825</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5,03%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,98%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>10,1%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3886</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1237</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10736</t>
+          <t>10711</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,22 +1477,22 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>8778</t>
+          <t>8894</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4395</t>
+          <t>4477</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15680</t>
+          <t>17053</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,79%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1897</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>6706</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>4,55%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>3384</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>966</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>9527</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>3,48%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>9,79%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1813</t>
+          <t>3667</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>713</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7431</t>
+          <t>9871</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>5197</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>1953</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12140</t>
+          <t>11897</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>12881</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7297</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>20887</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>8,74%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>4,95%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>14,17%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>4827</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1946</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>10360</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>4,96%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>5216</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>2080</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>11274</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>5,02%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>2,0%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>10,65%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>12494</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>6944</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>21230</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>8,37%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>4,65%</t>
-        </is>
-      </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>17320</t>
+          <t>18096</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>10404</t>
+          <t>10715</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>26612</t>
+          <t>27226</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,84%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>25999</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>17999</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>38549</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>17,64%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>12,21%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>26,16%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>14651</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>8933</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>21413</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>15,06%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>9,18%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>22,02%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>27899</t>
+          <t>15407</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18698</t>
+          <t>9618</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42960</t>
+          <t>22485</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>42550</t>
+          <t>41406</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32052</t>
+          <t>30088</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60274</t>
+          <t>55720</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>22,17%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>102777</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>90560</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>112839</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>69,74%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>61,45%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>76,57%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>69513</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>60979</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>76628</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>71,47%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>62,69%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>78,78%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>103124</t>
+          <t>74540</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>89837</t>
+          <t>65908</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>113855</t>
+          <t>82958</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>71,74%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>172637</t>
+          <t>177317</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>155999</t>
+          <t>163069</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>186360</t>
+          <t>191107</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>70,04%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>76,05%</t>
         </is>
       </c>
     </row>
@@ -1967,57 +1967,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>147368</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>147368</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>147368</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>97266</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>97266</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>97266</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>149215</t>
+          <t>103909</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>149215</t>
+          <t>103909</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>149215</t>
+          <t>103909</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>246482</t>
+          <t>251277</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>246482</t>
+          <t>251277</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>246482</t>
+          <t>251277</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>424</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,97%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>2552</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>569</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>7610</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,16%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>6,45%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>2748</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>802</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2311</t>
+          <t>7970</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>3171</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>967</t>
+          <t>890</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8325</t>
+          <t>8697</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>913</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>4682</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>4,56%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>2258</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>6935</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1,91%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>5,88%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>2277</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>363</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4008</t>
+          <t>6978</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>3161</t>
+          <t>3191</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>750</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8383</t>
+          <t>8145</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>816</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>7649</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2,94%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>7,44%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>5495</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1551</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>10696</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>4,66%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>9,06%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3160</t>
+          <t>5586</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>844</t>
+          <t>2560</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7479</t>
+          <t>10525</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>8655</t>
+          <t>8604</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4167</t>
+          <t>4214</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>14921</t>
+          <t>15011</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>7,83%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>24770</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>16621</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>37270</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>24,11%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>16,18%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>36,27%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>17323</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>7533</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>28177</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>14,68%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>6,38%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>23,88%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>24912</t>
+          <t>15027</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16368</t>
+          <t>9454</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37630</t>
+          <t>21279</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>42235</t>
+          <t>39797</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>25021</t>
+          <t>28753</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>58162</t>
+          <t>53848</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>28,1%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>73625</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>61059</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>82368</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>71,65%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>59,42%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>80,16%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>90382</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>77800</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>106262</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>76,59%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>65,93%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>90,05%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>79505</t>
+          <t>63259</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>67059</t>
+          <t>55552</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>89131</t>
+          <t>69873</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>62,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>169887</t>
+          <t>136884</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>153120</t>
+          <t>122700</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>191020</t>
+          <t>149024</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,46%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>77,76%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>102750</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>102750</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>102750</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>118009</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>118009</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>118009</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>108964</t>
+          <t>88897</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>108964</t>
+          <t>88897</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>108964</t>
+          <t>88897</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>226973</t>
+          <t>191647</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>226973</t>
+          <t>191647</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>226973</t>
+          <t>191647</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>4459</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1517</t>
+          <t>1484</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8769</t>
+          <t>8315</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>4014</t>
+          <t>4552</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1564</t>
+          <t>1676</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8383</t>
+          <t>9874</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>8473</t>
+          <t>8682</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4567</t>
+          <t>4703</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14479</t>
+          <t>15247</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,99%</t>
         </is>
       </c>
     </row>
@@ -2879,107 +2879,107 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>475</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>6294</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>6,91%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>1661</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>5933</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>6,15%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1661</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>477</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5452</t>
+          <t>6543</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -2992,72 +2992,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>3064</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>889</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>7500</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>3,37%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>8,24%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>5162</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>2078</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>10342</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>5,39%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>2,17%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>10,8%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3108</t>
+          <t>5241</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>829</t>
+          <t>2437</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7617</t>
+          <t>11019</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>8270</t>
+          <t>8305</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4405</t>
+          <t>4301</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>14613</t>
+          <t>14388</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -3105,72 +3105,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>12341</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>7184</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>18655</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>13,55%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>7,89%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>20,49%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>14821</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>9717</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>22286</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>15,48%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>15277</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>10123</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>22575</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>15,32%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>10,15%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>23,27%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>12907</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>7508</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>19330</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>13,38%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>7,78%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>27728</t>
+          <t>27618</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>19624</t>
+          <t>20289</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>36632</t>
+          <t>37714</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,77%</t>
         </is>
       </c>
     </row>
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>69481</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>61922</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>76218</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>76,32%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>68,01%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>83,72%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>71320</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>63380</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>78385</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>74,48%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>66,18%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>81,85%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>74781</t>
+          <t>74674</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>67677</t>
+          <t>66912</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>82185</t>
+          <t>81614</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>74,87%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>67,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>146101</t>
+          <t>144155</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>135569</t>
+          <t>132685</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>156185</t>
+          <t>154135</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>80,79%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>91044</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>91044</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>91044</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>131</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>95763</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>95763</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>95763</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>96471</t>
+          <t>99744</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>96471</t>
+          <t>99744</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>96471</t>
+          <t>99744</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>192234</t>
+          <t>190788</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>192234</t>
+          <t>190788</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>192234</t>
+          <t>190788</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3448,72 +3448,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>11270</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>5845</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>19657</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>2,68%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>4,68%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>14977</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>9075</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>23044</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>6,24%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>11109</t>
+          <t>15748</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>6326</t>
+          <t>9301</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>20142</t>
+          <t>23629</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>26086</t>
+          <t>27018</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>17479</t>
+          <t>18209</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>35125</t>
+          <t>37634</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -3561,72 +3561,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>6021</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>2555</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>11959</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>2,85%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>7328</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>3486</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>13845</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>1,99%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>3,75%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>5559</t>
+          <t>7790</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2430</t>
+          <t>3587</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>11051</t>
+          <t>14538</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>12888</t>
+          <t>13811</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>7609</t>
+          <t>8214</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>21008</t>
+          <t>22530</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -3674,72 +3674,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>23637</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>15174</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>33778</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>5,63%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>3,61%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>8,04%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>18326</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>11385</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>26668</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>4,96%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>3,08%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>7,22%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>28416</t>
+          <t>19065</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>18315</t>
+          <t>12402</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>49434</t>
+          <t>27356</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>46742</t>
+          <t>42702</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>34783</t>
+          <t>32389</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>68958</t>
+          <t>57482</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -3787,72 +3787,72 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>76865</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>61815</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>97418</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>18,3%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>14,72%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>23,2%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>58055</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>43418</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>72831</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>15,73%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>11,76%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>19,73%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>79250</t>
+          <t>57670</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>63174</t>
+          <t>46454</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>101345</t>
+          <t>69768</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>137305</t>
+          <t>134535</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>115800</t>
+          <t>114712</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>163058</t>
+          <t>156284</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,15%</t>
         </is>
       </c>
     </row>
@@ -3900,72 +3900,72 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>302191</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>278960</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>319865</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>71,95%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>66,42%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>76,16%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>340</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>270465</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>253007</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>295159</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>73,27%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>68,54%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>79,96%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>352</t>
-        </is>
-      </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>315390</t>
+          <t>255180</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>289031</t>
+          <t>240268</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>336001</t>
+          <t>269836</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>71,72%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>67,59%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>585855</t>
+          <t>557371</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>555292</t>
+          <t>533483</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>615138</t>
+          <t>581580</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>71,88%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>75,0%</t>
         </is>
       </c>
     </row>
@@ -4013,57 +4013,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>489</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>419984</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>419984</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>419984</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>475</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>369151</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>369151</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>369151</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>489</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>439724</t>
+          <t>355453</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>439724</t>
+          <t>355453</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>439724</t>
+          <t>355453</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>808876</t>
+          <t>775437</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>808876</t>
+          <t>775437</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>808876</t>
+          <t>775437</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
